--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G115"/>
+  <dimension ref="A1:G109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,20 +473,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>9amHealth</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
+          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
         </is>
       </c>
     </row>
@@ -561,47 +561,47 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aec208cdfd014f62</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4b12692ab49b7bf</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
         </is>
       </c>
     </row>
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
+          <t>Senior Backend Developer- Dallas, TX</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
+          <t>https://www.indeed.com/viewjob?jk=4e1c501899b24f6d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Backend Developer- Dallas, TX</t>
+          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -692,11 +692,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1c501899b24f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fullstack Engineer- Dallas, TX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fb1aacdf7b0187</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Fullstack Engineer- Dallas, TX</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=e8fb1aacdf7b0187</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr Data and Technology Analyst- Division of International Finance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, Glue, Lambda, API Gateway, RDS, Hadoop, HDFS, Hive, HBase, Impala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=777a27d0953faa85</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
+          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer Payments</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b8be749b58fda2</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HR AI/ML Engineer II</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Airbus</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Factory, Databricks, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3aa6bbabb3cbca2a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Production Engineer - Java Full Stack</t>
+          <t>Senior Java AWS Developer Payments</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a46943935a118c1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3b8be749b58fda2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Production Engineer - Java Full Stack</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=0a46943935a118c1</t>
         </is>
       </c>
     </row>
@@ -1868,17 +1868,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977965b62176a35b</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Constellation Brands</t>
+          <t>Colgate-Palmolive</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, RDS, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b8eb1b9b5c5757b</t>
+          <t>https://www.indeed.com/viewjob?jk=977965b62176a35b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (5+ years)</t>
+          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Foresite Labs</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, GCP, Spark, Scala, ETL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bd97d667dce4191</t>
+          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e24ee36e8cb7cb</t>
+          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Majesco Migration - Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Erie, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=8eef2c3133811ae9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Azure DevOps Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Assurant</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>API Gateway, RDS, Azure, MongoDB, CI/CD, Jenkins, Azure DevOps, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f808a6e0a9a9c0</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Majesco Migration - Data Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef2c3133811ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Azure DevOps, Maven</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63bd8141f670af91</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, GCP, Scala, Data Modeling, ETL, ELT, REST API integration, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=27cf68a988ace4d9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Associate, Snowflake Data Engineer – BTO</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Data Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e3555786ca60d7</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=987c15f4b88f3b87</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f42d634adbe30d12</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2cadc43695155d56</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (.NET / Azure) - Contract (1099)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Very LLC</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, DynamoDB, Azure Cosmos DB, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,67 +3681,67 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e8cc15987f9633</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI Application Developer III</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e147f982e60dddd</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI Application Developer III -Houston, TX</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Cotiviti</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ade1e18d7133f7cc</t>
+          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Sr. Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>Illumio</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,67 +3786,67 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=a132e788c3dae9fd</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Manufacturing Systems Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>voestalpine</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago Heights, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, ETL, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14943e02ccca3aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Mutual of Enumclaw Insurance</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Enumclaw, WA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Cloud Field, Consulting Sales Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Fortinet</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, DynamoDB, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e2605e226b8d2e7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Platform Reliability Engineer – Data, Content &amp; Analytics (Hybrid)</t>
+          <t>Data Architect – R01565081</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Securian Financial</t>
+          <t>Brillio LLC</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, Tableau, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43204d9b47ac68cd</t>
+          <t>https://www.indeed.com/viewjob?jk=331a50f67e92c5e5</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>TypeScript Backend Architect</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mutual of Enumclaw Insurance</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Enumclaw, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,34 +3986,34 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Kafka, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
+          <t>https://www.indeed.com/viewjob?jk=806e6d1aea5231f7</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>V&amp;V Engineer – AI - Driven Testing &amp; Validation</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e6e47c4f9f9521bc</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cotiviti</t>
+          <t>Paramount Global US Inc</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
+          <t>AWS, Hadoop, HDFS, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
+          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Architect – R01565081</t>
+          <t>SAP NS2 Sr. Security Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Brillio LLC</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331a50f67e92c5e5</t>
+          <t>https://www.indeed.com/viewjob?jk=ca031bcce448fdbd</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>TypeScript Backend Architect</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Kafka, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=806e6d1aea5231f7</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>V&amp;V Engineer – AI - Driven Testing &amp; Validation</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e47c4f9f9521bc</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Paramount Global US Inc</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, HDFS, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
+          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Security Engineer</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,217 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca031bcce448fdbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Full stack (Angular/Java) (Remote)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>The Home Depot</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Cloud Storage, Scala, MySQL, ETL, GitHub Actions, Docker, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f7acce88de00e812</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Business Intelligence SME – MicroStrategy</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>A1fed</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Scala, SQL Server, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f40722715cc5f7ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineer, People Innovation Labs</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G109"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,12 +643,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Developer- Dallas, TX</t>
+          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e1c501899b24f6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
+          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. APIM Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, GCP, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=254d152353d4fb63</t>
+          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
         </is>
       </c>
     </row>
@@ -998,20 +998,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Fullstack Engineer- Dallas, TX</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, PostgreSQL, MongoDB, DynamoDB, NoSQL, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8fb1aacdf7b0187</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Data and Technology Analyst- Division of International Finance</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, RDS, Hadoop, HDFS, Hive, HBase, Impala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,19 +1161,19 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777a27d0953faa85</t>
+          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1182,11 +1182,11 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,102 +1441,102 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Hadoop, Spark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ec1df703d4c5e04</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer Payments</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3b8be749b58fda2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Production Engineer - Java Full Stack</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, IAM, RDS, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a46943935a118c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Colgate-Palmolive</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, NoSQL, ETL, ELT, dbt</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=977965b62176a35b</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,102 +1966,102 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33c42309195b0e99</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Development Engineer in Test (SDET) – ML &amp; LLM Systems</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47435f267ff5c4f3</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Majesco Migration - Data Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Erie, PA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8eef2c3133811ae9</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Data Modeling, ETL, ELT, REST API integration, Power BI, Tableau</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27cf68a988ace4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior Data Engineer - Python, CI/CD</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987c15f4b88f3b87</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3575,671 +3575,6 @@
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Next Gen Software Solutions</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Berkeley Heights, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Cotiviti</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Spark, Scala, Oracle, SQL Server, ETL, Python, SQL, Java</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=21a4c2b4ffe6da75</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sr. Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Illumio</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a132e788c3dae9fd</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>objectways</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Mutual of Enumclaw Insurance</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Enumclaw, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Scala, Snowflake, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8cfe3ebca43d1190</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Cloud Field, Consulting Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Fortinet</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, DynamoDB, Terraform, AWS CloudFormation, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2605e226b8d2e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Data Architect – R01565081</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Brillio LLC</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Ashburn, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Snowflake, ETL, ELT, dbt, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=331a50f67e92c5e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>TypeScript Backend Architect</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Kafka, DynamoDB, NoSQL, Splunk, CI/CD, Jenkins, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=806e6d1aea5231f7</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>V&amp;V Engineer – AI - Driven Testing &amp; Validation</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, MLOps, MLflow, CI/CD, Jenkins, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6e47c4f9f9521bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Paramount Global US Inc</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Hadoop, HDFS, Spark, Scala, NoSQL, ETL, Talend, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=741583eb645f2b61</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>SAP NS2 Sr. Security Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca031bcce448fdbd</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Data Engineer, People Innovation Labs</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
         </is>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Hyperlight</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Ciklum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
+          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,19 +1651,19 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Marks IT Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Python, CI/CD</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>Senior Data Engineer - Dbt, CI/CD</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer-Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer, People Innovation Labs</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,87 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
+          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
+          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
+          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
+          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>Sr. Data Engineer, Enterprise - Slack</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Senior Software Engineer (Data Engineering)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Kohl's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Senior Software Engineer, MLOps</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,19 +1686,19 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>Select Computing, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Dbt, CI/CD</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e080fd03b67aa874</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,59 +3261,59 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer-Infrastructure</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior Data Engineer – Palantir Foundry</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>objectways</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer, People Innovation Labs</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,41 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6324c917198667</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
+          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Dallas County</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
+          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
+          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>DELVIX EDGE</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Linux CloudSystem Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Tecnologix Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ciklum</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a79e1bdde74b9d64</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Full Stack AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
+          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
+          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
+          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Scientist / Software Engineer - REMOTE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Binary Defense</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
+          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
         </is>
       </c>
     </row>
@@ -1448,60 +1448,60 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, MLOps</t>
+          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Rivian</t>
+          <t>Premier Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MLOps, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc794d07abe54d18</t>
+          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Application Developer - ETL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>QVC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Quality Assurance Automation Engineer-SBA REMOTE</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Select Computing, Inc.</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, API Gateway, RDS, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd90ecd4db68aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer with Snowflake (Specialist - Architecture)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Google Cloud Platform, GCP, Scala, Snowflake, MongoDB, Jenkins, GitHub Actions</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e85e605fbf14aff</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer III - Various Locations!</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>Halff</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,19 +2106,19 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Mainframe Professionals(Devops Architect, System automation, Performance engineer)- REMOTE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Marks IT Solutions</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fd17dcf4756a3fb</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Dolese Bros.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Azure Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Northern Trust Corp.</t>
+          <t>Münchener Rückversicherungs-Gesellschaft</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, Scala, Kafka, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb63b2457498a97c</t>
+          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Next Gen Software Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer-Infrastructure</t>
+          <t>API Automation</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, People Innovation Labs</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>OpenAI</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Palantir Foundry</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>objectways</t>
+          <t>Amplify</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cloud Storage, Spark, PySpark, Scala, Dimensional Modeling, ELT, CI/CD</t>
+          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3435,181 +3435,6 @@
         </is>
       </c>
       <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b037ba4140056f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineer, People Innovation Labs</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
         </is>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G86"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
+          <t>Analyst, Information Technology (Data Engineer)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Oriental Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0000001423.AI ENGINEER II.INFO TECH - DATA AND AI</t>
+          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Dallas County</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e292fecba5a3f54</t>
+          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
         </is>
       </c>
     </row>
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Linux CloudSystem Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DELVIX EDGE</t>
+          <t>Tecnologix Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3059a32608f8fae5</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Linux CloudSystem Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tecnologix Limited</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Bridgeway Benefit Technologies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Maple Shade, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Hyperlight</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ad143bf215dca2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Sr Data and Technology Analyst- Division of International Finance</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hyperlight</t>
+          <t>Board of Governors of the Federal Reserve System</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
+          <t>AWS, Glue, Lambda, API Gateway, RDS, Hadoop, HDFS, Hive, HBase, Impala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
+          <t>https://www.indeed.com/viewjob?jk=777a27d0953faa85</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
+          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Agentic AI Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kohl's</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, GCP, Flume, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c990ef27a139b23</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SENIOR DATA ARCHITECT - DIGITAL HEALTH</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Premier Health</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, BigQuery, Hadoop, Impala, Spark, Scala, Kafka, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=292331db8e10cf3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Senior Java Full Stack Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,52 +1501,52 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ce81ab377f28cb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Application Developer - ETL</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QVC</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f171de2a8d453f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=4b60af712b26a5dd</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Kimball Midwest</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer - Various Locations!</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15e9c504e5bf2337</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Business Systems Data Analyst / Power BI &amp; Fabric Developer III - Various Locations!</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Halff</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Dataflow, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c78c332d8a817d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Cloud Engineer IV</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,67 +2736,67 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>BI Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>McLane Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Temple, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Data Modeling, ETL, ELT, REST API integration, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=27cf68a988ace4d9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dolese Bros.</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, MLOps</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=424490df54f1f917</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,42 +3076,42 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Münchener Rückversicherungs-Gesellschaft</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, ETL, ELT, dbt, MLflow, CI/CD, Docker, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a2a57e7a76cf6ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer (Ab Initio, OzoneCH, Flink) | Berkeley Heights, NJ (5 Days Onsite) | W2 &amp; Fulltime</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Next Gen Software Solutions</t>
+          <t>GeoLogics Corporation</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Sterling Heights, MI, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, ETL, CI/CD, Docker, Kubernetes, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,67 +3156,67 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01b3676cfd5abae5</t>
+          <t>https://www.indeed.com/viewjob?jk=987c15f4b88f3b87</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineer-Infrastructure</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,59 +3261,59 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>API Automation</t>
+          <t>Linux Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+          <t>https://www.indeed.com/viewjob?jk=bdd9a77f8957015f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer, People Innovation Labs</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>OpenAI</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SQL/Power BI Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Amplify</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,17 +3426,332 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Associate Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Bridgewater, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8a4fe70a1dad5e45</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Tax Platform</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Alpaca</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Step Functions, Spark, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4beb98cf5a2cf48</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Cloud Field, Consulting Sales Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Fortinet</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, DynamoDB, Terraform, AWS CloudFormation, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e2605e226b8d2e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Reporting Engineer - Hybrid / Remote</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Surgery Partners</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Data Engineer, People Innovation Labs</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>OpenAI</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>API Automation</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SQL/Power BI Developer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Intellibee Inc</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Raleigh, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Amplify</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Brooklyn, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. Security Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca031bcce448fdbd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9amHealth</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
+          <t>https://www.indeed.com/viewjob?jk=e58ec0c3fb594e76</t>
         </is>
       </c>
     </row>
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>9amHealth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
+          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
+          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Analyst, Information Technology (Data Engineer)</t>
+          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Oriental Bank</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
+          <t>Analyst, Information Technology (Data Engineer)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Oriental Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
         </is>
       </c>
     </row>
@@ -783,25 +783,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Linux CloudSystem Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tecnologix Limited</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Linux CloudSystem Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Tecnologix Limited</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bridgeway Benefit Technologies</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Maple Shade, NJ, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Azure, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93da204448eced35</t>
+          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hyperlight</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Hyperlight</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Data and Technology Analyst- Division of International Finance</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Board of Governors of the Federal Reserve System</t>
+          <t>Arbitration Forums Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, API Gateway, RDS, Hadoop, HDFS, Hive, HBase, Impala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777a27d0953faa85</t>
+          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f6f96717fce7453</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fdd121cf76131f</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, RDS, Databricks, Spark, Scala, Kafka, MongoDB</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,42 +1056,42 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a51a69b48d4433f</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer, Enterprise - Slack</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,139 +1396,139 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Azure, GCP, Hadoop, Spark, Scala, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d23fbcc1f6757ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Engineer</t>
+          <t>Jr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Motorola Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Kinesis, RDS, Spark, Scala, Kafka, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ce81ab377f28cb</t>
+          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,24 +1536,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b60af712b26a5dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
@@ -1768,20 +1768,20 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Kimball Midwest</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Dataflow, Spark, PySpark, Scala, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b74bdf4ebde15159</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,29 +1921,29 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer IV</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cee754bcb206b7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>University of Miami</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Software Engineer (Backend, Python) - Content Understanding</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Scribd, Inc.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,67 +2701,67 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>BI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>McLane Company</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Temple, TX, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Data Modeling, ETL, ELT, REST API integration, Power BI, Tableau</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27cf68a988ace4d9</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>BI Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Augeo Affinity Marketing, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53b1dbd9dfc660aa</t>
+          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Tableau Developer- Remote</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,102 +3086,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pacers Sports &amp; Entertainment</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Modeler</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GeoLogics Corporation</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sterling Heights, MI, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Medallion Architecture, Hadoop, Spark, Scala, Oracle, Dimensional Modeling</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987c15f4b88f3b87</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior AI Reconciliation Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,94 +3226,94 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>BI Developer</t>
+          <t>API Automation</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Linux Systems Engineer</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd9a77f8957015f</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer-Infrastructure</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
+          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior CloudOps Engineer</t>
+          <t>SQL/Power BI Developer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,392 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Associate Test Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Bridgewater, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8a4fe70a1dad5e45</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Tax Platform</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Alpaca</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, Step Functions, Spark, Scala, Kafka, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b4beb98cf5a2cf48</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Cloud Field, Consulting Sales Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Fortinet</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Oracle, PostgreSQL, DynamoDB, Terraform, AWS CloudFormation, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e2605e226b8d2e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineer, People Innovation Labs</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>OpenAI</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Spark, Scala, Snowflake, ETL</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24ca3431dcbcd257</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>API Automation</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Amplify</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Brooklyn, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, RDS, Scala, Snowflake, PostgreSQL, DynamoDB, Terraform, Docker, Datadog</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24cdc5d33ce531fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>SAP NS2 Sr. Security Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Herndon, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ca031bcce448fdbd</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,20 +508,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9amHealth</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,59 +531,59 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=204b0fbde6acaec8</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analyst, Information Technology (Data Engineer)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Oriental Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Sr. Consultant - Fullstack GenAI Enablement</t>
+          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, API Gateway, ECS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c9240c1f60b916</t>
+          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Analyst, Information Technology (Data Engineer)</t>
+          <t>Data Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Oriental Bank</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Senior Software Engineer - Cloud Applications</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>10Beauty</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Burlington, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
+          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Linux CloudSystem Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Tecnologix Limited</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Linux CloudSystem Engineer</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tecnologix Limited</t>
+          <t>Hyperlight</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CMT Services INC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=735a340ab156699c</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fdd121cf76131f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer- Remote US</t>
+          <t>Senior Software Engineer, Backend Services</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>The University of Chicago</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
+          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hyperlight</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,102 +951,102 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Industrial Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Arbitration Forums Inc.</t>
+          <t>Esi solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sisters, OR, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca67cc261c055a24</t>
+          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Agentic AI Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fdd121cf76131f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr IT Architect- Database</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEODIS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Agentic AI Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,102 +1161,102 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=380cf25a1caed88b</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e9d4486acb8678</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,137 +1266,137 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bbb011f9ed9bce</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Senior Development Security Operations Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>American Tower</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbab770adbb8a52e</t>
+          <t>https://www.indeed.com/viewjob?jk=eed0a361f2bb8836</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Full Stack AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Kafka, PostgreSQL, MongoDB, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0eeb94a75d20a86</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer - REMOTE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Binary Defense</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, Azure, GCP, Vertex AI, Hadoop, Spark, NoSQL, Power BI, Tableau</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=decf8fd160fb3bfb</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,94 +1476,94 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=503059911980b460</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jr. Data Engineer</t>
+          <t>Data and AI Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, PostgreSQL, Dimensional Modeling, Kimball, Snowflake Schema, Dimension Tables</t>
+          <t>RDS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74de48d3af0aad60</t>
+          <t>https://www.indeed.com/viewjob?jk=747301f11f5bc958</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Senior Data &amp; Security Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=696a66668bdedd2b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Motorola Solutions</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Azure, GCP, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8955fa66fad71b11</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Senior Solutions Architect - HR Technology</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II-Software Development</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=4b60af712b26a5dd</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=6b525c6918aa7bd0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
@@ -1973,25 +1973,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Data Engineer (AWS Redshift/Python)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>University of Miami</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, Azure, Scala, MongoDB, NoSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c486a5510b1decbc</t>
+          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75411ef68bb2570e</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=476610eade6186c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Pluto TV</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>West Hollywood, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f17865b87f690bc6</t>
+          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Solutions Engineer - Data Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20459d59093bf9bd</t>
+          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>AI Data Analyst</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Averna</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, BigQuery, Vertex AI, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12dec38d572dde69</t>
+          <t>https://www.indeed.com/viewjob?jk=09c247b71f8052bf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>General Dynamics Information Technology</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d562fe192869c0e</t>
+          <t>https://www.indeed.com/viewjob?jk=837203d21b6808cb</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c9a1ae81f793646</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5863d525ca41f5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,172 +2316,172 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e4cdf0234a46615</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ad137f2c49da8bb</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d002e82641911ed2</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46fb0e086ae4f0e3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6725c8d5ffa853</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99737475fca40d8b</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,847 +2526,147 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b74a0d4661cfffa</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Software Engineer - Mid/Sr.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Git, Datadog</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8957e81f116b84</t>
+          <t>https://www.indeed.com/viewjob?jk=7ae5bcd4793ab2b8</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df2181db2e5a2dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>API Automation</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c06ae27381f690e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend, Python) - Content Understanding</t>
+          <t>Senior Cloud Infrastructure Engineer (MSP Experience Required)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Scribd, Inc.</t>
+          <t>QIT SOLUTIONS</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, ECS, IAM, RDS, Azure, Databricks, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Terraform, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc3126e4cf6aee72</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Cincinnati, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>The New IEM, LLC</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior AI Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>EchoStar</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Englewood, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Pluto TV</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>West Hollywood, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Solutions Engineer - Data Engineering</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SHI International</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Azure Data Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Township of Hamilton, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ae87fbdbeca42ee9</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Pacers Sports &amp; Entertainment</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Senior AI Reconciliation Analyst</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Dave</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Tableau Developer- Remote</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Cystems Logic Inc</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>BI Developer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Augeo Affinity Marketing, Inc.</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Saint Paul, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Dataflow, Scala, Snowflake, SQL Server, Dimensional Modeling, Snowflake Schema, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33a301267b057586</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Data &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Alternate Solutions Health Network</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Software Engineer-Infrastructure</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior CloudOps Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Alexandria, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>API Automation</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=963a094838b9c1b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>SQL/Power BI Developer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Intellibee Inc</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b078bd21fd98c8d7</t>
+          <t>https://www.indeed.com/viewjob?jk=2a59a68b637a5948</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-14.xlsx
+++ b/results/job_matches_2026-05-14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Royal Caribbean Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Miramar, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS, SNS, API Gateway</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e58ec0c3fb594e76</t>
+          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analyst, Information Technology (Data Engineer)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Oriental Bank</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>San Juan, PR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.8</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
+          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8b0be90fe0a7694</t>
+          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Analyst, Information Technology (Data Engineer)</t>
+          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Oriental Bank</t>
+          <t>Mizuho Bank</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Juan, PR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,112 +556,112 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, S3, IAM, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fc8c26cf52dfcdf</t>
+          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Credit Risk Technology – Risk Data Integration Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mizuho Bank</t>
+          <t>Vari</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coppell, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1705eebaf5cd797</t>
+          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - Hybrid / Remote</t>
+          <t>Linux CloudSystem Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Surgery Partners</t>
+          <t>Tecnologix Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Event Hubs, Unity Catalog, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1741157e1f1cd7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vari</t>
+          <t>Trane Technologies</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Coppell, TX, US USA</t>
+          <t>Davidson, NC, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, BigQuery, Snowflake, SQL Server, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Redshift, Google Cloud Platform, GCP, BigQuery, HDFS, Hive, MapReduce, HBase, YARN</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2810f8864fd85dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=1592c4516bdc87a8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Senior DataOps Engineer- Remote US</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Smile Digital Health</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Burlington, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdc7cb699ca48c49</t>
+          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Cloud Applications</t>
+          <t>Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10Beauty</t>
+          <t>Hyperlight</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25dd86b5d7c3e977</t>
+          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Linux CloudSystem Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tecnologix Limited</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e0f807a114ce5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5fdd121cf76131f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DataOps Engineer- Remote US</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Smile Digital Health</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, GCP, Spark, Scala, DataOps, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b4e77c5e89765ba</t>
+          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data &amp; AI Engineer</t>
+          <t>Industrial Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hyperlight</t>
+          <t>Esi solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Sisters, OR, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, S3, RDS, Photon, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3d8a2e8f953d307</t>
+          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Agentic AI Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5fdd121cf76131f</t>
+          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Backend Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>The University of Chicago</t>
+          <t>Filevine</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lambda, Kinesis, Step Functions, S3, ECS, IAM, RDS, Azure, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=282052d4249e7a38</t>
+          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr IT Architect- Database</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>GEODIS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Brentwood, TN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Hadoop, Hive, MapReduce, Spark, Scala</t>
+          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4967ce59e3591939</t>
+          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Industrial Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Esi solutions</t>
+          <t>Progyny</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sisters, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4677bac9c152c55d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agentic AI Data Engineer</t>
+          <t>Senior AWS Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf62a60610273c1a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Modem Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Filevine</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Streams/Tasks, Data Modeling</t>
+          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8615d09cb38109c0</t>
+          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Sr IT Architect- Database</t>
+          <t>PLTR Developer- Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEODIS</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Brentwood, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, Azure, BigQuery, Scala, Kafka, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383ad7639607ff42</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Databricks Senior Data &amp; AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Progyny</t>
+          <t>V2 Strategic Advisors</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, RDS, Snowflake, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5dcacd0f80c521d</t>
+          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior AWS Infrastructure Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, RDS, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9baca6f377f5dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Modem Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, Databricks, Spark, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08060b468511a1d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLTR Developer- Remote</t>
+          <t>Senior Platform Engineer - Global CI/CD Platform</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cystems Logic Inc</t>
+          <t>Transamerica</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cedar Rapids, IA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb17df245873596</t>
+          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Databricks Senior Data &amp; AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>V2 Strategic Advisors</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05f974dbef0d4638</t>
+          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Development Security Operations Engineer</t>
+          <t>Senior Data Engineer, AI &amp; Data Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Tower</t>
+          <t>Leadfeeder</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eed0a361f2bb8836</t>
+          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdc756e0a30786a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9719511fa10c7f9c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,217 +1361,217 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Data Lake Storage, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd0eed32fbae1e5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6df8bc0328124d57</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Global CI/CD Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Transamerica</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cedar Rapids, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Scala, Splunk, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a30cd040a7f97b4</t>
+          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8369c074d102201</t>
+          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Littleton, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, BigQuery, Scala, Snowflake, ETL, dbt, CI/CD</t>
+          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=503059911980b460</t>
+          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data and AI Architect</t>
+          <t>Systems &amp; Cloud Infrastructure Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Kretek International</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Moorpark, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=747301f11f5bc958</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Security Architect</t>
+          <t>EverCommerce - Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=696a66668bdedd2b</t>
+          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, AI &amp; Data Platform</t>
+          <t>AI Application Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Leadfeeder</t>
+          <t>Lenovo</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, BigQuery, Scala, Snowflake, dbt</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, PostgreSQL, MySQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,137 +1581,137 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9c87ec5354ee008</t>
+          <t>https://www.indeed.com/viewjob?jk=581828717e283b41</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - HR Technology</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Electronic Arts</t>
+          <t>Riverain Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4da44f9db3087ad</t>
+          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer II-Software Development</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>The New IEM, LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, PostgreSQL, MySQL, ELT, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7108d25e7d7c8254</t>
+          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>EchoStar</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b60af712b26a5dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Pacers Sports &amp; Entertainment</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,194 +1721,194 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=828e55e71d22edfc</t>
+          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Reporting Engineer - Hybrid / Remote</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Surgery Partners</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Scala, CI/CD, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b525c6918aa7bd0</t>
+          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer (Hybrid In-Office / Remote)</t>
+          <t>Senior AI Reconciliation Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=291bcfc0c31c7b7b</t>
+          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Engineer II, Lennar.com</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Lennar</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Littleton, CO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Spark Streaming, Kafka, PostgreSQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b3c61819ab6737c</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6bfbe4b81a06a3</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Systems &amp; Cloud Infrastructure Engineer</t>
+          <t>Tableau Developer- Remote</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kretek International</t>
+          <t>Cystems Logic Inc</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Moorpark, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Splunk, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d5b7958721b0c5</t>
+          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EverCommerce - Senior Data Engineer</t>
+          <t>Data &amp; Integrations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Evercommerce</t>
+          <t>Alternate Solutions Health Network</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Athena, S3, RDS, Databricks, Scala, Kafka, Data Modeling, dbt, Airflow</t>
+          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=158bcbd65f733f36</t>
+          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Riverain Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1917,11 +1917,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Hive, Scala, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077145bd3bd32de2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Software Engineer-Infrastructure</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ada48dbcb0fb083</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (AWS Redshift/Python)</t>
+          <t>Senior CloudOps Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Alexandria, VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,672 +2001,147 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2522a67f157402a5</t>
+          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>The New IEM, LLC</t>
+          <t>Rocket</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, Dimensional Modeling, Star Schema, Fact Tables, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9daec59612efc459</t>
+          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Platform Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EchoStar</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Englewood, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, Scala, Star Schema, ETL, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f6853815a5710a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2fbb73301c658fc3</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Pluto TV</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>West Hollywood, CA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Hadoop, Spark, Kafka, Data Modeling, ETL, ELT, Docker</t>
+          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24191e9278bc5735</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Solutions Engineer - Data Engineering</t>
+          <t>API Automation</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Scala, SQL Server, Data Modeling, ETL</t>
+          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53d6063859712a59</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>AI Data Analyst</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Averna</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>RDS, BigQuery, Vertex AI, Scala, Data Modeling, Power BI, Tableau, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=09c247b71f8052bf</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Cloud Data Architect</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>General Dynamics Information Technology</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, Oracle, SQL Server, MySQL, DynamoDB</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=837203d21b6808cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Pacers Sports &amp; Entertainment</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Data Modeling, Dimensional Modeling, ELT, dbt, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e91c364ef51d1d33</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Reporting Engineer - Hybrid / Remote</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Surgery Partners</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Dataflow, Snowflake, Dimensional Modeling, Star Schema, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=432d70e30d357218</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Senior AI Reconciliation Analyst</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Dave</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, dbt, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0320187ce551a7ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Tableau Developer- Remote</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Cystems Logic Inc</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, ETL, Power BI</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f20fb10dc8288bcf</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Data &amp; Integrations Engineer</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Alternate Solutions Health Network</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Lambda, SQS, API Gateway, RDS, Scala, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=41c501bbcf2c51c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Sr. Automation Engineer, Falcon Complete (Remote)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, IAM, RDS, Scala, Kafka, Cassandra, NoSQL, CI/CD, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fdebadd59b18aca7</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Software Engineer-Infrastructure</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Cisco</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Research Triangle Park, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Kafka, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e8e5dd47c42fc9</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Senior CloudOps Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Alexandria, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Oracle, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Terraform, Git</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4931dc95bcbec0b</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Rocket</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Detroit, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Scala, NoSQL, Data Modeling, ETL, ELT, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-05-13</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=345945d4c9f90358</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Software Engineer - Mid/Sr.</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, CI/CD, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ae5bcd4793ab2b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>DevOps Platform Engineer (GitHub Actions &amp; Enterprise Git Governance)</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Recutify Inc.</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Spark, PySpark, Pentaho, CI/CD, Jenkins, GitHub Actions, Jenkins, pytest</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdb736ffad340c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>API Automation</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Azure, Kafka, Cassandra, Data Modeling, ETL, CI/CD, Kubernetes, AKS, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=5e8f6975673f15cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Senior Cloud Infrastructure Engineer (MSP Experience Required)</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>QIT SOLUTIONS</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Terraform, AKS</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a59a68b637a5948</t>
         </is>
       </c>
     </row>
